--- a/Data/gp2_bodyweight_v2.xlsx
+++ b/Data/gp2_bodyweight_v2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Guinea-Pig-data_2\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2600B4EB-F010-4FA8-8608-8D4F0A613E9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26F69C72-422D-4B1B-9748-48C5ECF4EFAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{78382E1D-78A1-456C-A7ED-1874B01E5345}"/>
   </bookViews>
@@ -477,15 +477,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB0BA55F-BF94-4AB5-B1AD-C1FAE1A2BD26}">
   <dimension ref="A1:G801"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -508,7 +508,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -531,7 +531,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -554,7 +554,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -577,7 +577,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -600,7 +600,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -623,7 +623,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -646,7 +646,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -669,7 +669,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -692,7 +692,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
@@ -715,7 +715,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
@@ -738,7 +738,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
@@ -761,7 +761,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>7</v>
       </c>
@@ -784,7 +784,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>7</v>
       </c>
@@ -807,7 +807,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>7</v>
       </c>
@@ -830,7 +830,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>7</v>
       </c>
@@ -853,7 +853,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>7</v>
       </c>
@@ -876,7 +876,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>7</v>
       </c>
@@ -899,7 +899,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>7</v>
       </c>
@@ -922,7 +922,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>7</v>
       </c>
@@ -945,7 +945,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>7</v>
       </c>
@@ -968,7 +968,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>7</v>
       </c>
@@ -991,7 +991,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>7</v>
       </c>
@@ -1014,7 +1014,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>7</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>7</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>7</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>7</v>
       </c>
@@ -1106,7 +1106,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>7</v>
       </c>
@@ -1129,7 +1129,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>7</v>
       </c>
@@ -1152,7 +1152,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>7</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>7</v>
       </c>
@@ -1198,7 +1198,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>7</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>7</v>
       </c>
@@ -1244,7 +1244,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>7</v>
       </c>
@@ -1267,7 +1267,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>7</v>
       </c>
@@ -1290,7 +1290,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>7</v>
       </c>
@@ -1313,7 +1313,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>7</v>
       </c>
@@ -1336,7 +1336,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>7</v>
       </c>
@@ -1359,7 +1359,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>7</v>
       </c>
@@ -1382,7 +1382,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>7</v>
       </c>
@@ -1405,7 +1405,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>7</v>
       </c>
@@ -1428,7 +1428,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>7</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>7</v>
       </c>
@@ -1474,7 +1474,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>7</v>
       </c>
@@ -1497,7 +1497,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>7</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>7</v>
       </c>
@@ -1543,7 +1543,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>7</v>
       </c>
@@ -1566,7 +1566,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>7</v>
       </c>
@@ -1589,7 +1589,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>7</v>
       </c>
@@ -1612,7 +1612,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>7</v>
       </c>
@@ -1635,7 +1635,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>7</v>
       </c>
@@ -1658,7 +1658,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>7</v>
       </c>
@@ -1681,7 +1681,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>7</v>
       </c>
@@ -1704,7 +1704,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>7</v>
       </c>
@@ -1727,7 +1727,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>7</v>
       </c>
@@ -1750,7 +1750,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>7</v>
       </c>
@@ -1773,7 +1773,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>7</v>
       </c>
@@ -1796,7 +1796,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>7</v>
       </c>
@@ -1819,7 +1819,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>7</v>
       </c>
@@ -1842,7 +1842,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>7</v>
       </c>
@@ -1865,7 +1865,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>7</v>
       </c>
@@ -1888,7 +1888,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>7</v>
       </c>
@@ -1911,7 +1911,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>7</v>
       </c>
@@ -1934,7 +1934,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>7</v>
       </c>
@@ -1957,7 +1957,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>7</v>
       </c>
@@ -1980,7 +1980,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>7</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>7</v>
       </c>
@@ -2026,7 +2026,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>7</v>
       </c>
@@ -2049,7 +2049,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>7</v>
       </c>
@@ -2072,7 +2072,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>7</v>
       </c>
@@ -2095,7 +2095,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>7</v>
       </c>
@@ -2118,7 +2118,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>7</v>
       </c>
@@ -2141,7 +2141,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>7</v>
       </c>
@@ -2164,7 +2164,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>7</v>
       </c>
@@ -2187,7 +2187,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>7</v>
       </c>
@@ -2210,7 +2210,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>7</v>
       </c>
@@ -2233,7 +2233,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>7</v>
       </c>
@@ -2256,7 +2256,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>7</v>
       </c>
@@ -2279,7 +2279,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>7</v>
       </c>
@@ -2302,7 +2302,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>7</v>
       </c>
@@ -2325,7 +2325,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>7</v>
       </c>
@@ -2348,7 +2348,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>7</v>
       </c>
@@ -2371,7 +2371,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>7</v>
       </c>
@@ -2394,7 +2394,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>7</v>
       </c>
@@ -2417,7 +2417,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>7</v>
       </c>
@@ -2440,7 +2440,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>7</v>
       </c>
@@ -2463,7 +2463,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>7</v>
       </c>
@@ -2486,7 +2486,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>7</v>
       </c>
@@ -2509,7 +2509,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>7</v>
       </c>
@@ -2532,7 +2532,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>7</v>
       </c>
@@ -2555,7 +2555,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>7</v>
       </c>
@@ -2578,7 +2578,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>7</v>
       </c>
@@ -2601,7 +2601,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>7</v>
       </c>
@@ -2624,7 +2624,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>7</v>
       </c>
@@ -2647,7 +2647,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>7</v>
       </c>
@@ -2670,7 +2670,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>7</v>
       </c>
@@ -2693,7 +2693,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>7</v>
       </c>
@@ -2716,7 +2716,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>7</v>
       </c>
@@ -2739,7 +2739,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>7</v>
       </c>
@@ -2762,7 +2762,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>7</v>
       </c>
@@ -2785,7 +2785,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>7</v>
       </c>
@@ -2808,7 +2808,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>7</v>
       </c>
@@ -2831,7 +2831,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>7</v>
       </c>
@@ -2854,7 +2854,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>7</v>
       </c>
@@ -2877,7 +2877,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>7</v>
       </c>
@@ -2900,7 +2900,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>7</v>
       </c>
@@ -2923,7 +2923,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>7</v>
       </c>
@@ -2946,7 +2946,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>7</v>
       </c>
@@ -2969,7 +2969,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>7</v>
       </c>
@@ -2992,7 +2992,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>7</v>
       </c>
@@ -3015,7 +3015,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>7</v>
       </c>
@@ -3038,7 +3038,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>7</v>
       </c>
@@ -3061,7 +3061,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>7</v>
       </c>
@@ -3084,7 +3084,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>7</v>
       </c>
@@ -3107,7 +3107,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>7</v>
       </c>
@@ -3130,7 +3130,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>7</v>
       </c>
@@ -3153,7 +3153,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>7</v>
       </c>
@@ -3176,7 +3176,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>7</v>
       </c>
@@ -3199,7 +3199,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>7</v>
       </c>
@@ -3222,7 +3222,7 @@
         <v>685.47</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>7</v>
       </c>
@@ -3245,7 +3245,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>7</v>
       </c>
@@ -3268,7 +3268,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>7</v>
       </c>
@@ -3291,7 +3291,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>7</v>
       </c>
@@ -3314,7 +3314,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>7</v>
       </c>
@@ -3337,7 +3337,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>7</v>
       </c>
@@ -3360,7 +3360,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>7</v>
       </c>
@@ -3383,7 +3383,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>7</v>
       </c>
@@ -3406,7 +3406,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>7</v>
       </c>
@@ -3429,7 +3429,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>7</v>
       </c>
@@ -3452,7 +3452,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>7</v>
       </c>
@@ -3475,7 +3475,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>7</v>
       </c>
@@ -3498,7 +3498,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>7</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>7</v>
       </c>
@@ -3544,7 +3544,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>7</v>
       </c>
@@ -3567,7 +3567,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>7</v>
       </c>
@@ -3590,7 +3590,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>7</v>
       </c>
@@ -3613,7 +3613,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>7</v>
       </c>
@@ -3636,7 +3636,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>7</v>
       </c>
@@ -3659,7 +3659,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>7</v>
       </c>
@@ -3682,7 +3682,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>7</v>
       </c>
@@ -3705,7 +3705,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>7</v>
       </c>
@@ -3728,7 +3728,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>7</v>
       </c>
@@ -3751,7 +3751,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>7</v>
       </c>
@@ -3774,7 +3774,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>7</v>
       </c>
@@ -3797,7 +3797,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>7</v>
       </c>
@@ -3820,7 +3820,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>7</v>
       </c>
@@ -3843,7 +3843,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>7</v>
       </c>
@@ -3866,7 +3866,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>7</v>
       </c>
@@ -3889,7 +3889,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>7</v>
       </c>
@@ -3912,7 +3912,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>7</v>
       </c>
@@ -3935,7 +3935,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>7</v>
       </c>
@@ -3958,7 +3958,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>7</v>
       </c>
@@ -3981,7 +3981,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>7</v>
       </c>
@@ -4004,7 +4004,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>7</v>
       </c>
@@ -4027,7 +4027,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>7</v>
       </c>
@@ -4050,7 +4050,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>7</v>
       </c>
@@ -4073,7 +4073,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>7</v>
       </c>
@@ -4096,7 +4096,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>7</v>
       </c>
@@ -4119,7 +4119,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>7</v>
       </c>
@@ -4142,7 +4142,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>7</v>
       </c>
@@ -4165,7 +4165,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>7</v>
       </c>
@@ -4188,7 +4188,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>7</v>
       </c>
@@ -4211,7 +4211,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>7</v>
       </c>
@@ -4234,7 +4234,7 @@
         <v>509.5</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>7</v>
       </c>
@@ -4257,7 +4257,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>7</v>
       </c>
@@ -4280,7 +4280,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>7</v>
       </c>
@@ -4303,7 +4303,7 @@
         <v>658.5</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>7</v>
       </c>
@@ -4326,7 +4326,7 @@
         <v>729.5</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>7</v>
       </c>
@@ -4349,7 +4349,7 @@
         <v>569.5</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>7</v>
       </c>
@@ -4372,7 +4372,7 @@
         <v>548.5</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>7</v>
       </c>
@@ -4395,7 +4395,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>7</v>
       </c>
@@ -4418,7 +4418,7 @@
         <v>736.5</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>7</v>
       </c>
@@ -4441,7 +4441,7 @@
         <v>548.5</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>7</v>
       </c>
@@ -4464,7 +4464,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>7</v>
       </c>
@@ -4487,7 +4487,7 @@
         <v>713.5</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>7</v>
       </c>
@@ -4510,7 +4510,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>7</v>
       </c>
@@ -4533,7 +4533,7 @@
         <v>665.5</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>7</v>
       </c>
@@ -4556,7 +4556,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>7</v>
       </c>
@@ -4579,7 +4579,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>7</v>
       </c>
@@ -4602,7 +4602,7 @@
         <v>694.5</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>7</v>
       </c>
@@ -4625,7 +4625,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>7</v>
       </c>
@@ -4648,7 +4648,7 @@
         <v>607.5</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>7</v>
       </c>
@@ -4671,7 +4671,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>7</v>
       </c>
@@ -4694,7 +4694,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>7</v>
       </c>
@@ -4717,7 +4717,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>7</v>
       </c>
@@ -4740,7 +4740,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>7</v>
       </c>
@@ -4763,7 +4763,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>7</v>
       </c>
@@ -4786,7 +4786,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>7</v>
       </c>
@@ -4809,7 +4809,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>7</v>
       </c>
@@ -4832,7 +4832,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>7</v>
       </c>
@@ -4855,7 +4855,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>7</v>
       </c>
@@ -4878,7 +4878,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>7</v>
       </c>
@@ -4901,7 +4901,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>7</v>
       </c>
@@ -4924,7 +4924,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>7</v>
       </c>
@@ -4947,7 +4947,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>7</v>
       </c>
@@ -4970,7 +4970,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>7</v>
       </c>
@@ -4993,7 +4993,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>7</v>
       </c>
@@ -5016,7 +5016,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>7</v>
       </c>
@@ -5039,7 +5039,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>7</v>
       </c>
@@ -5062,7 +5062,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>7</v>
       </c>
@@ -5085,7 +5085,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>7</v>
       </c>
@@ -5108,7 +5108,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>18</v>
       </c>
@@ -5131,7 +5131,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>18</v>
       </c>
@@ -5154,7 +5154,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>18</v>
       </c>
@@ -5177,7 +5177,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>18</v>
       </c>
@@ -5200,7 +5200,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>18</v>
       </c>
@@ -5223,7 +5223,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>18</v>
       </c>
@@ -5246,7 +5246,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>18</v>
       </c>
@@ -5269,7 +5269,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>18</v>
       </c>
@@ -5292,7 +5292,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>18</v>
       </c>
@@ -5315,7 +5315,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>18</v>
       </c>
@@ -5338,7 +5338,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>18</v>
       </c>
@@ -5361,7 +5361,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>18</v>
       </c>
@@ -5384,7 +5384,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>18</v>
       </c>
@@ -5407,7 +5407,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>18</v>
       </c>
@@ -5430,7 +5430,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>18</v>
       </c>
@@ -5453,7 +5453,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>18</v>
       </c>
@@ -5476,7 +5476,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>18</v>
       </c>
@@ -5499,7 +5499,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>18</v>
       </c>
@@ -5522,7 +5522,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>18</v>
       </c>
@@ -5545,7 +5545,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>18</v>
       </c>
@@ -5568,7 +5568,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>18</v>
       </c>
@@ -5591,7 +5591,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>18</v>
       </c>
@@ -5614,7 +5614,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>18</v>
       </c>
@@ -5637,7 +5637,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>18</v>
       </c>
@@ -5660,7 +5660,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>18</v>
       </c>
@@ -5683,7 +5683,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>18</v>
       </c>
@@ -5706,7 +5706,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>18</v>
       </c>
@@ -5729,7 +5729,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
         <v>18</v>
       </c>
@@ -5752,7 +5752,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>18</v>
       </c>
@@ -5775,7 +5775,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>18</v>
       </c>
@@ -5798,7 +5798,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>18</v>
       </c>
@@ -5821,7 +5821,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>18</v>
       </c>
@@ -5844,7 +5844,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>18</v>
       </c>
@@ -5867,7 +5867,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>18</v>
       </c>
@@ -5890,7 +5890,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>18</v>
       </c>
@@ -5913,7 +5913,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>18</v>
       </c>
@@ -5936,7 +5936,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
         <v>18</v>
       </c>
@@ -5959,7 +5959,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
         <v>18</v>
       </c>
@@ -5982,7 +5982,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
         <v>18</v>
       </c>
@@ -6005,7 +6005,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>18</v>
       </c>
@@ -6028,7 +6028,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
         <v>18</v>
       </c>
@@ -6051,7 +6051,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
         <v>18</v>
       </c>
@@ -6074,7 +6074,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>18</v>
       </c>
@@ -6097,7 +6097,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>18</v>
       </c>
@@ -6120,7 +6120,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
         <v>18</v>
       </c>
@@ -6143,7 +6143,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
         <v>18</v>
       </c>
@@ -6166,7 +6166,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
         <v>18</v>
       </c>
@@ -6189,7 +6189,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
         <v>18</v>
       </c>
@@ -6212,7 +6212,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
         <v>18</v>
       </c>
@@ -6235,7 +6235,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
         <v>18</v>
       </c>
@@ -6258,7 +6258,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
         <v>18</v>
       </c>
@@ -6281,7 +6281,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
         <v>18</v>
       </c>
@@ -6304,7 +6304,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
         <v>18</v>
       </c>
@@ -6327,7 +6327,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
         <v>18</v>
       </c>
@@ -6350,7 +6350,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
         <v>18</v>
       </c>
@@ -6373,7 +6373,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
         <v>18</v>
       </c>
@@ -6396,7 +6396,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>18</v>
       </c>
@@ -6419,7 +6419,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>18</v>
       </c>
@@ -6442,7 +6442,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>18</v>
       </c>
@@ -6465,7 +6465,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
         <v>18</v>
       </c>
@@ -6488,7 +6488,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>18</v>
       </c>
@@ -6511,7 +6511,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
         <v>18</v>
       </c>
@@ -6534,7 +6534,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
         <v>18</v>
       </c>
@@ -6557,7 +6557,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
         <v>18</v>
       </c>
@@ -6580,7 +6580,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
         <v>18</v>
       </c>
@@ -6603,7 +6603,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
         <v>18</v>
       </c>
@@ -6626,7 +6626,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
         <v>18</v>
       </c>
@@ -6649,7 +6649,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
         <v>18</v>
       </c>
@@ -6672,7 +6672,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
         <v>18</v>
       </c>
@@ -6695,7 +6695,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>18</v>
       </c>
@@ -6718,7 +6718,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>18</v>
       </c>
@@ -6741,7 +6741,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
         <v>18</v>
       </c>
@@ -6764,7 +6764,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
         <v>18</v>
       </c>
@@ -6787,7 +6787,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
         <v>18</v>
       </c>
@@ -6810,7 +6810,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
         <v>18</v>
       </c>
@@ -6833,7 +6833,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
         <v>18</v>
       </c>
@@ -6856,7 +6856,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
         <v>18</v>
       </c>
@@ -6879,7 +6879,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
         <v>18</v>
       </c>
@@ -6902,7 +6902,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
         <v>18</v>
       </c>
@@ -6925,7 +6925,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
         <v>18</v>
       </c>
@@ -6948,7 +6948,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
         <v>18</v>
       </c>
@@ -6971,7 +6971,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
         <v>18</v>
       </c>
@@ -6994,7 +6994,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
         <v>18</v>
       </c>
@@ -7017,7 +7017,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
         <v>18</v>
       </c>
@@ -7040,7 +7040,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
         <v>18</v>
       </c>
@@ -7063,7 +7063,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
         <v>18</v>
       </c>
@@ -7086,7 +7086,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
         <v>18</v>
       </c>
@@ -7109,7 +7109,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
         <v>18</v>
       </c>
@@ -7132,7 +7132,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
         <v>18</v>
       </c>
@@ -7155,7 +7155,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
         <v>18</v>
       </c>
@@ -7178,7 +7178,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
         <v>18</v>
       </c>
@@ -7201,7 +7201,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
         <v>18</v>
       </c>
@@ -7224,7 +7224,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
         <v>18</v>
       </c>
@@ -7247,7 +7247,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
         <v>18</v>
       </c>
@@ -7270,7 +7270,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
         <v>18</v>
       </c>
@@ -7293,7 +7293,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
         <v>18</v>
       </c>
@@ -7316,7 +7316,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
         <v>18</v>
       </c>
@@ -7339,7 +7339,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
         <v>18</v>
       </c>
@@ -7362,7 +7362,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
         <v>18</v>
       </c>
@@ -7385,7 +7385,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
         <v>18</v>
       </c>
@@ -7408,7 +7408,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
         <v>18</v>
       </c>
@@ -7431,7 +7431,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
         <v>18</v>
       </c>
@@ -7454,7 +7454,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
         <v>18</v>
       </c>
@@ -7477,7 +7477,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
         <v>18</v>
       </c>
@@ -7500,7 +7500,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
         <v>18</v>
       </c>
@@ -7523,7 +7523,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
         <v>18</v>
       </c>
@@ -7546,7 +7546,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
         <v>18</v>
       </c>
@@ -7569,7 +7569,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
         <v>18</v>
       </c>
@@ -7592,7 +7592,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
         <v>18</v>
       </c>
@@ -7615,7 +7615,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
         <v>18</v>
       </c>
@@ -7638,7 +7638,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
         <v>18</v>
       </c>
@@ -7661,7 +7661,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
         <v>18</v>
       </c>
@@ -7684,7 +7684,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
         <v>18</v>
       </c>
@@ -7707,7 +7707,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
         <v>18</v>
       </c>
@@ -7730,7 +7730,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
         <v>18</v>
       </c>
@@ -7753,7 +7753,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
         <v>18</v>
       </c>
@@ -7776,7 +7776,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
         <v>18</v>
       </c>
@@ -7799,7 +7799,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
         <v>18</v>
       </c>
@@ -7822,7 +7822,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
         <v>18</v>
       </c>
@@ -7845,7 +7845,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
         <v>18</v>
       </c>
@@ -7868,7 +7868,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
         <v>18</v>
       </c>
@@ -7891,7 +7891,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
         <v>18</v>
       </c>
@@ -7914,7 +7914,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
         <v>18</v>
       </c>
@@ -7937,7 +7937,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
         <v>18</v>
       </c>
@@ -7960,7 +7960,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
         <v>18</v>
       </c>
@@ -7983,7 +7983,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
         <v>18</v>
       </c>
@@ -8006,7 +8006,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
         <v>18</v>
       </c>
@@ -8029,7 +8029,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
         <v>18</v>
       </c>
@@ -8052,7 +8052,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
         <v>18</v>
       </c>
@@ -8075,7 +8075,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
         <v>18</v>
       </c>
@@ -8098,7 +8098,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
         <v>18</v>
       </c>
@@ -8121,7 +8121,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
         <v>18</v>
       </c>
@@ -8144,7 +8144,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
         <v>18</v>
       </c>
@@ -8167,7 +8167,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
         <v>18</v>
       </c>
@@ -8190,7 +8190,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
         <v>18</v>
       </c>
@@ -8213,7 +8213,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
         <v>18</v>
       </c>
@@ -8236,7 +8236,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
         <v>18</v>
       </c>
@@ -8259,7 +8259,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
         <v>18</v>
       </c>
@@ -8282,7 +8282,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
         <v>18</v>
       </c>
@@ -8305,7 +8305,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
         <v>18</v>
       </c>
@@ -8328,7 +8328,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
         <v>18</v>
       </c>
@@ -8351,7 +8351,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
         <v>18</v>
       </c>
@@ -8374,7 +8374,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
         <v>18</v>
       </c>
@@ -8397,7 +8397,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
         <v>18</v>
       </c>
@@ -8420,7 +8420,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
         <v>18</v>
       </c>
@@ -8443,7 +8443,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
         <v>18</v>
       </c>
@@ -8466,7 +8466,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
         <v>18</v>
       </c>
@@ -8489,7 +8489,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
         <v>18</v>
       </c>
@@ -8512,7 +8512,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
         <v>18</v>
       </c>
@@ -8535,7 +8535,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
         <v>18</v>
       </c>
@@ -8558,7 +8558,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
         <v>18</v>
       </c>
@@ -8581,7 +8581,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
         <v>18</v>
       </c>
@@ -8604,7 +8604,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
         <v>18</v>
       </c>
@@ -8627,7 +8627,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
         <v>18</v>
       </c>
@@ -8650,7 +8650,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
         <v>18</v>
       </c>
@@ -8673,7 +8673,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="s">
         <v>18</v>
       </c>
@@ -8696,7 +8696,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="s">
         <v>18</v>
       </c>
@@ -8719,7 +8719,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="s">
         <v>18</v>
       </c>
@@ -8742,7 +8742,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A360" s="1" t="s">
         <v>18</v>
       </c>
@@ -8765,7 +8765,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="s">
         <v>18</v>
       </c>
@@ -8788,7 +8788,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="s">
         <v>18</v>
       </c>
@@ -8811,7 +8811,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="363" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
         <v>18</v>
       </c>
@@ -8834,7 +8834,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="s">
         <v>18</v>
       </c>
@@ -8857,7 +8857,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A365" s="1" t="s">
         <v>18</v>
       </c>
@@ -8880,7 +8880,7 @@
         <v>625.5</v>
       </c>
     </row>
-    <row r="366" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="s">
         <v>18</v>
       </c>
@@ -8903,7 +8903,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="s">
         <v>18</v>
       </c>
@@ -8926,7 +8926,7 @@
         <v>602.5</v>
       </c>
     </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="s">
         <v>18</v>
       </c>
@@ -8949,7 +8949,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="s">
         <v>18</v>
       </c>
@@ -8972,7 +8972,7 @@
         <v>700.5</v>
       </c>
     </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="s">
         <v>18</v>
       </c>
@@ -8995,7 +8995,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="s">
         <v>18</v>
       </c>
@@ -9018,7 +9018,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
         <v>18</v>
       </c>
@@ -9041,7 +9041,7 @@
         <v>536.5</v>
       </c>
     </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="s">
         <v>18</v>
       </c>
@@ -9064,7 +9064,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="s">
         <v>18</v>
       </c>
@@ -9087,7 +9087,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A375" s="1" t="s">
         <v>18</v>
       </c>
@@ -9110,7 +9110,7 @@
         <v>681.5</v>
       </c>
     </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A376" s="1" t="s">
         <v>18</v>
       </c>
@@ -9133,7 +9133,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A377" s="1" t="s">
         <v>18</v>
       </c>
@@ -9156,7 +9156,7 @@
         <v>646.5</v>
       </c>
     </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="s">
         <v>18</v>
       </c>
@@ -9179,7 +9179,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="s">
         <v>18</v>
       </c>
@@ -9202,7 +9202,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="s">
         <v>18</v>
       </c>
@@ -9225,7 +9225,7 @@
         <v>729.5</v>
       </c>
     </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A381" s="1" t="s">
         <v>18</v>
       </c>
@@ -9248,7 +9248,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A382" s="1" t="s">
         <v>18</v>
       </c>
@@ -9271,7 +9271,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="s">
         <v>18</v>
       </c>
@@ -9294,7 +9294,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="384" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="s">
         <v>18</v>
       </c>
@@ -9317,7 +9317,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="s">
         <v>18</v>
       </c>
@@ -9340,7 +9340,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A386" s="1" t="s">
         <v>18</v>
       </c>
@@ -9363,7 +9363,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="s">
         <v>18</v>
       </c>
@@ -9386,7 +9386,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="388" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="s">
         <v>18</v>
       </c>
@@ -9409,7 +9409,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A389" s="1" t="s">
         <v>18</v>
       </c>
@@ -9432,7 +9432,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A390" s="1" t="s">
         <v>18</v>
       </c>
@@ -9455,7 +9455,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="s">
         <v>18</v>
       </c>
@@ -9478,7 +9478,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="s">
         <v>18</v>
       </c>
@@ -9501,7 +9501,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="s">
         <v>18</v>
       </c>
@@ -9524,7 +9524,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="s">
         <v>18</v>
       </c>
@@ -9547,7 +9547,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="s">
         <v>18</v>
       </c>
@@ -9570,7 +9570,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A396" s="1" t="s">
         <v>18</v>
       </c>
@@ -9593,7 +9593,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A397" s="1" t="s">
         <v>18</v>
       </c>
@@ -9616,7 +9616,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A398" s="1" t="s">
         <v>18</v>
       </c>
@@ -9639,7 +9639,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="s">
         <v>18</v>
       </c>
@@ -9662,7 +9662,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="400" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A400" s="1" t="s">
         <v>18</v>
       </c>
@@ -9685,7 +9685,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A401" s="1" t="s">
         <v>18</v>
       </c>
@@ -9708,7 +9708,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="402" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A402" s="1" t="s">
         <v>20</v>
       </c>
@@ -9731,7 +9731,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="403" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A403" s="1" t="s">
         <v>20</v>
       </c>
@@ -9754,7 +9754,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="404" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A404" s="1" t="s">
         <v>20</v>
       </c>
@@ -9777,7 +9777,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="405" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A405" s="1" t="s">
         <v>20</v>
       </c>
@@ -9800,7 +9800,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="406" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A406" s="1" t="s">
         <v>20</v>
       </c>
@@ -9823,7 +9823,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="407" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A407" s="1" t="s">
         <v>20</v>
       </c>
@@ -9846,7 +9846,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="408" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A408" s="1" t="s">
         <v>20</v>
       </c>
@@ -9869,7 +9869,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A409" s="1" t="s">
         <v>20</v>
       </c>
@@ -9892,7 +9892,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A410" s="1" t="s">
         <v>20</v>
       </c>
@@ -9915,7 +9915,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="411" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A411" s="1" t="s">
         <v>20</v>
       </c>
@@ -9938,7 +9938,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="412" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A412" s="1" t="s">
         <v>20</v>
       </c>
@@ -9961,7 +9961,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="413" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A413" s="1" t="s">
         <v>20</v>
       </c>
@@ -9984,7 +9984,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="414" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A414" s="1" t="s">
         <v>20</v>
       </c>
@@ -10007,7 +10007,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="415" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A415" s="1" t="s">
         <v>20</v>
       </c>
@@ -10030,7 +10030,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="416" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A416" s="1" t="s">
         <v>20</v>
       </c>
@@ -10053,7 +10053,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A417" s="1" t="s">
         <v>20</v>
       </c>
@@ -10076,7 +10076,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A418" s="1" t="s">
         <v>20</v>
       </c>
@@ -10099,7 +10099,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="419" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A419" s="1" t="s">
         <v>20</v>
       </c>
@@ -10122,7 +10122,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A420" s="1" t="s">
         <v>20</v>
       </c>
@@ -10145,7 +10145,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="421" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A421" s="1" t="s">
         <v>20</v>
       </c>
@@ -10168,7 +10168,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="422" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A422" s="1" t="s">
         <v>20</v>
       </c>
@@ -10191,7 +10191,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A423" s="1" t="s">
         <v>20</v>
       </c>
@@ -10214,7 +10214,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="424" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A424" s="1" t="s">
         <v>20</v>
       </c>
@@ -10237,7 +10237,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A425" s="1" t="s">
         <v>20</v>
       </c>
@@ -10260,7 +10260,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="426" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A426" s="1" t="s">
         <v>20</v>
       </c>
@@ -10283,7 +10283,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="427" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A427" s="1" t="s">
         <v>20</v>
       </c>
@@ -10306,7 +10306,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="428" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A428" s="1" t="s">
         <v>20</v>
       </c>
@@ -10329,7 +10329,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A429" s="1" t="s">
         <v>20</v>
       </c>
@@ -10352,7 +10352,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="430" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A430" s="1" t="s">
         <v>20</v>
       </c>
@@ -10375,7 +10375,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A431" s="1" t="s">
         <v>20</v>
       </c>
@@ -10398,7 +10398,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A432" s="1" t="s">
         <v>20</v>
       </c>
@@ -10421,7 +10421,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A433" s="1" t="s">
         <v>20</v>
       </c>
@@ -10444,7 +10444,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A434" s="1" t="s">
         <v>20</v>
       </c>
@@ -10467,7 +10467,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A435" s="1" t="s">
         <v>20</v>
       </c>
@@ -10490,7 +10490,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A436" s="1" t="s">
         <v>20</v>
       </c>
@@ -10513,7 +10513,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A437" s="1" t="s">
         <v>20</v>
       </c>
@@ -10536,7 +10536,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A438" s="1" t="s">
         <v>20</v>
       </c>
@@ -10559,7 +10559,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A439" s="1" t="s">
         <v>20</v>
       </c>
@@ -10582,7 +10582,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A440" s="1" t="s">
         <v>20</v>
       </c>
@@ -10605,7 +10605,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A441" s="1" t="s">
         <v>20</v>
       </c>
@@ -10628,7 +10628,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A442" s="1" t="s">
         <v>20</v>
       </c>
@@ -10651,7 +10651,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A443" s="1" t="s">
         <v>20</v>
       </c>
@@ -10674,7 +10674,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A444" s="1" t="s">
         <v>20</v>
       </c>
@@ -10697,7 +10697,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A445" s="1" t="s">
         <v>20</v>
       </c>
@@ -10720,7 +10720,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A446" s="1" t="s">
         <v>20</v>
       </c>
@@ -10743,7 +10743,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="447" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A447" s="1" t="s">
         <v>20</v>
       </c>
@@ -10766,7 +10766,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="448" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A448" s="1" t="s">
         <v>20</v>
       </c>
@@ -10789,7 +10789,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A449" s="1" t="s">
         <v>20</v>
       </c>
@@ -10812,7 +10812,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A450" s="1" t="s">
         <v>20</v>
       </c>
@@ -10835,7 +10835,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A451" s="1" t="s">
         <v>20</v>
       </c>
@@ -10858,7 +10858,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="452" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A452" s="1" t="s">
         <v>20</v>
       </c>
@@ -10881,7 +10881,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A453" s="1" t="s">
         <v>20</v>
       </c>
@@ -10904,7 +10904,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="454" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A454" s="1" t="s">
         <v>20</v>
       </c>
@@ -10927,7 +10927,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="455" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A455" s="1" t="s">
         <v>20</v>
       </c>
@@ -10950,7 +10950,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="456" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A456" s="1" t="s">
         <v>20</v>
       </c>
@@ -10973,7 +10973,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="457" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A457" s="1" t="s">
         <v>20</v>
       </c>
@@ -10996,7 +10996,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="458" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A458" s="1" t="s">
         <v>20</v>
       </c>
@@ -11019,7 +11019,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="459" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A459" s="1" t="s">
         <v>20</v>
       </c>
@@ -11042,7 +11042,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="460" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A460" s="1" t="s">
         <v>20</v>
       </c>
@@ -11065,7 +11065,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="461" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A461" s="1" t="s">
         <v>20</v>
       </c>
@@ -11088,7 +11088,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="462" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A462" s="1" t="s">
         <v>20</v>
       </c>
@@ -11111,7 +11111,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="463" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A463" s="1" t="s">
         <v>20</v>
       </c>
@@ -11134,7 +11134,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="464" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A464" s="1" t="s">
         <v>20</v>
       </c>
@@ -11157,7 +11157,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="465" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A465" s="1" t="s">
         <v>20</v>
       </c>
@@ -11180,7 +11180,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="466" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A466" s="1" t="s">
         <v>20</v>
       </c>
@@ -11203,7 +11203,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="467" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A467" s="1" t="s">
         <v>20</v>
       </c>
@@ -11226,7 +11226,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="468" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A468" s="1" t="s">
         <v>20</v>
       </c>
@@ -11249,7 +11249,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="469" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A469" s="1" t="s">
         <v>20</v>
       </c>
@@ -11272,7 +11272,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="470" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A470" s="1" t="s">
         <v>20</v>
       </c>
@@ -11295,7 +11295,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="471" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A471" s="1" t="s">
         <v>20</v>
       </c>
@@ -11318,7 +11318,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="472" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A472" s="1" t="s">
         <v>20</v>
       </c>
@@ -11341,7 +11341,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="473" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A473" s="1" t="s">
         <v>20</v>
       </c>
@@ -11364,7 +11364,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="474" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A474" s="1" t="s">
         <v>20</v>
       </c>
@@ -11387,7 +11387,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="475" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A475" s="1" t="s">
         <v>20</v>
       </c>
@@ -11410,7 +11410,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="476" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A476" s="1" t="s">
         <v>20</v>
       </c>
@@ -11433,7 +11433,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="477" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A477" s="1" t="s">
         <v>20</v>
       </c>
@@ -11456,7 +11456,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="478" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A478" s="1" t="s">
         <v>20</v>
       </c>
@@ -11479,7 +11479,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="479" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A479" s="1" t="s">
         <v>20</v>
       </c>
@@ -11502,7 +11502,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="480" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A480" s="1" t="s">
         <v>20</v>
       </c>
@@ -11525,7 +11525,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="481" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A481" s="1" t="s">
         <v>20</v>
       </c>
@@ -11548,7 +11548,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="482" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A482" s="1" t="s">
         <v>20</v>
       </c>
@@ -11571,7 +11571,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="483" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A483" s="1" t="s">
         <v>20</v>
       </c>
@@ -11594,7 +11594,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="484" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A484" s="1" t="s">
         <v>20</v>
       </c>
@@ -11617,7 +11617,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="485" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A485" s="1" t="s">
         <v>20</v>
       </c>
@@ -11640,7 +11640,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="486" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A486" s="1" t="s">
         <v>20</v>
       </c>
@@ -11663,7 +11663,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="487" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A487" s="1" t="s">
         <v>20</v>
       </c>
@@ -11686,7 +11686,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="488" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A488" s="1" t="s">
         <v>20</v>
       </c>
@@ -11709,7 +11709,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="489" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A489" s="1" t="s">
         <v>20</v>
       </c>
@@ -11732,7 +11732,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="490" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A490" s="1" t="s">
         <v>20</v>
       </c>
@@ -11755,7 +11755,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="491" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A491" s="1" t="s">
         <v>20</v>
       </c>
@@ -11778,7 +11778,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="492" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A492" s="1" t="s">
         <v>20</v>
       </c>
@@ -11801,7 +11801,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="493" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A493" s="1" t="s">
         <v>20</v>
       </c>
@@ -11824,7 +11824,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="494" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A494" s="1" t="s">
         <v>20</v>
       </c>
@@ -11847,7 +11847,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="495" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A495" s="1" t="s">
         <v>20</v>
       </c>
@@ -11870,7 +11870,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="496" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A496" s="1" t="s">
         <v>20</v>
       </c>
@@ -11893,7 +11893,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="497" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A497" s="1" t="s">
         <v>20</v>
       </c>
@@ -11916,7 +11916,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="498" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A498" s="1" t="s">
         <v>20</v>
       </c>
@@ -11939,7 +11939,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="499" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A499" s="1" t="s">
         <v>20</v>
       </c>
@@ -11962,7 +11962,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="500" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A500" s="1" t="s">
         <v>20</v>
       </c>
@@ -11985,7 +11985,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="501" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A501" s="1" t="s">
         <v>20</v>
       </c>
@@ -12008,7 +12008,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="502" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A502" s="1" t="s">
         <v>20</v>
       </c>
@@ -12031,7 +12031,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="503" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A503" s="1" t="s">
         <v>20</v>
       </c>
@@ -12054,7 +12054,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="504" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A504" s="1" t="s">
         <v>20</v>
       </c>
@@ -12077,7 +12077,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="505" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A505" s="1" t="s">
         <v>20</v>
       </c>
@@ -12100,7 +12100,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="506" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A506" s="1" t="s">
         <v>20</v>
       </c>
@@ -12123,7 +12123,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="507" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A507" s="1" t="s">
         <v>20</v>
       </c>
@@ -12146,7 +12146,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="508" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A508" s="1" t="s">
         <v>20</v>
       </c>
@@ -12169,7 +12169,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="509" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A509" s="1" t="s">
         <v>20</v>
       </c>
@@ -12192,7 +12192,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="510" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A510" s="1" t="s">
         <v>20</v>
       </c>
@@ -12215,7 +12215,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="511" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A511" s="1" t="s">
         <v>20</v>
       </c>
@@ -12238,7 +12238,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="512" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A512" s="1" t="s">
         <v>20</v>
       </c>
@@ -12261,7 +12261,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="513" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A513" s="1" t="s">
         <v>20</v>
       </c>
@@ -12284,7 +12284,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="514" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A514" s="1" t="s">
         <v>20</v>
       </c>
@@ -12307,7 +12307,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="515" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A515" s="1" t="s">
         <v>20</v>
       </c>
@@ -12330,7 +12330,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="516" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A516" s="1" t="s">
         <v>20</v>
       </c>
@@ -12353,7 +12353,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="517" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A517" s="1" t="s">
         <v>20</v>
       </c>
@@ -12376,7 +12376,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="518" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A518" s="1" t="s">
         <v>20</v>
       </c>
@@ -12399,7 +12399,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="519" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A519" s="1" t="s">
         <v>20</v>
       </c>
@@ -12422,7 +12422,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="520" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A520" s="1" t="s">
         <v>20</v>
       </c>
@@ -12445,7 +12445,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="521" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A521" s="1" t="s">
         <v>20</v>
       </c>
@@ -12468,7 +12468,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="522" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A522" s="1" t="s">
         <v>20</v>
       </c>
@@ -12491,7 +12491,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="523" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A523" s="1" t="s">
         <v>20</v>
       </c>
@@ -12514,7 +12514,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="524" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A524" s="1" t="s">
         <v>20</v>
       </c>
@@ -12537,7 +12537,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="525" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A525" s="1" t="s">
         <v>20</v>
       </c>
@@ -12560,7 +12560,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="526" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A526" s="1" t="s">
         <v>20</v>
       </c>
@@ -12583,7 +12583,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="527" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A527" s="1" t="s">
         <v>20</v>
       </c>
@@ -12606,7 +12606,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="528" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A528" s="1" t="s">
         <v>20</v>
       </c>
@@ -12629,7 +12629,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="529" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A529" s="1" t="s">
         <v>20</v>
       </c>
@@ -12652,7 +12652,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="530" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A530" s="1" t="s">
         <v>20</v>
       </c>
@@ -12675,7 +12675,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="531" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A531" s="1" t="s">
         <v>20</v>
       </c>
@@ -12698,7 +12698,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="532" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A532" s="1" t="s">
         <v>20</v>
       </c>
@@ -12721,7 +12721,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="533" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A533" s="1" t="s">
         <v>20</v>
       </c>
@@ -12744,7 +12744,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="534" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A534" s="1" t="s">
         <v>20</v>
       </c>
@@ -12767,7 +12767,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="535" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A535" s="1" t="s">
         <v>20</v>
       </c>
@@ -12790,7 +12790,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="536" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A536" s="1" t="s">
         <v>20</v>
       </c>
@@ -12813,7 +12813,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="537" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A537" s="1" t="s">
         <v>20</v>
       </c>
@@ -12836,7 +12836,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="538" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A538" s="1" t="s">
         <v>20</v>
       </c>
@@ -12859,7 +12859,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="539" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A539" s="1" t="s">
         <v>20</v>
       </c>
@@ -12882,7 +12882,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="540" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A540" s="1" t="s">
         <v>20</v>
       </c>
@@ -12905,7 +12905,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="541" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A541" s="1" t="s">
         <v>20</v>
       </c>
@@ -12928,7 +12928,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="542" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A542" s="1" t="s">
         <v>20</v>
       </c>
@@ -12951,7 +12951,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="543" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A543" s="1" t="s">
         <v>20</v>
       </c>
@@ -12974,7 +12974,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="544" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A544" s="1" t="s">
         <v>20</v>
       </c>
@@ -12997,7 +12997,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="545" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A545" s="1" t="s">
         <v>20</v>
       </c>
@@ -13020,7 +13020,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="546" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A546" s="1" t="s">
         <v>20</v>
       </c>
@@ -13043,7 +13043,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="547" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A547" s="1" t="s">
         <v>20</v>
       </c>
@@ -13066,7 +13066,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="548" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A548" s="1" t="s">
         <v>20</v>
       </c>
@@ -13089,7 +13089,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="549" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A549" s="1" t="s">
         <v>20</v>
       </c>
@@ -13112,7 +13112,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="550" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A550" s="1" t="s">
         <v>20</v>
       </c>
@@ -13135,7 +13135,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="551" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A551" s="1" t="s">
         <v>20</v>
       </c>
@@ -13158,7 +13158,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="552" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A552" s="1" t="s">
         <v>20</v>
       </c>
@@ -13181,7 +13181,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="553" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A553" s="1" t="s">
         <v>20</v>
       </c>
@@ -13204,7 +13204,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="554" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A554" s="1" t="s">
         <v>20</v>
       </c>
@@ -13227,7 +13227,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="555" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A555" s="1" t="s">
         <v>20</v>
       </c>
@@ -13250,7 +13250,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="556" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A556" s="1" t="s">
         <v>20</v>
       </c>
@@ -13273,7 +13273,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="557" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A557" s="1" t="s">
         <v>20</v>
       </c>
@@ -13296,7 +13296,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="558" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A558" s="1" t="s">
         <v>20</v>
       </c>
@@ -13319,7 +13319,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="559" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A559" s="1" t="s">
         <v>20</v>
       </c>
@@ -13342,7 +13342,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="560" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A560" s="1" t="s">
         <v>20</v>
       </c>
@@ -13365,7 +13365,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="561" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A561" s="1" t="s">
         <v>20</v>
       </c>
@@ -13388,7 +13388,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="562" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A562" s="1" t="s">
         <v>20</v>
       </c>
@@ -13411,7 +13411,7 @@
         <v>662.5</v>
       </c>
     </row>
-    <row r="563" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A563" s="1" t="s">
         <v>20</v>
       </c>
@@ -13434,7 +13434,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="564" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A564" s="1" t="s">
         <v>20</v>
       </c>
@@ -13457,7 +13457,7 @@
         <v>808.5</v>
       </c>
     </row>
-    <row r="565" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A565" s="1" t="s">
         <v>20</v>
       </c>
@@ -13480,7 +13480,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="566" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A566" s="1" t="s">
         <v>20</v>
       </c>
@@ -13503,7 +13503,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="567" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A567" s="1" t="s">
         <v>20</v>
       </c>
@@ -13526,7 +13526,7 @@
         <v>563.5</v>
       </c>
     </row>
-    <row r="568" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A568" s="1" t="s">
         <v>20</v>
       </c>
@@ -13549,7 +13549,7 @@
         <v>771.5</v>
       </c>
     </row>
-    <row r="569" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A569" s="1" t="s">
         <v>20</v>
       </c>
@@ -13572,7 +13572,7 @@
         <v>706.5</v>
       </c>
     </row>
-    <row r="570" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A570" s="1" t="s">
         <v>20</v>
       </c>
@@ -13595,7 +13595,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="571" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A571" s="1" t="s">
         <v>20</v>
       </c>
@@ -13618,7 +13618,7 @@
         <v>673.5</v>
       </c>
     </row>
-    <row r="572" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A572" s="1" t="s">
         <v>20</v>
       </c>
@@ -13641,7 +13641,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="573" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A573" s="1" t="s">
         <v>20</v>
       </c>
@@ -13664,7 +13664,7 @@
         <v>728.5</v>
       </c>
     </row>
-    <row r="574" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A574" s="1" t="s">
         <v>20</v>
       </c>
@@ -13687,7 +13687,7 @@
         <v>628.5</v>
       </c>
     </row>
-    <row r="575" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A575" s="1" t="s">
         <v>20</v>
       </c>
@@ -13710,7 +13710,7 @@
         <v>719.5</v>
       </c>
     </row>
-    <row r="576" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A576" s="1" t="s">
         <v>20</v>
       </c>
@@ -13733,7 +13733,7 @@
         <v>672.5</v>
       </c>
     </row>
-    <row r="577" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A577" s="1" t="s">
         <v>20</v>
       </c>
@@ -13756,7 +13756,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="578" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A578" s="1" t="s">
         <v>20</v>
       </c>
@@ -13779,7 +13779,7 @@
         <v>568.5</v>
       </c>
     </row>
-    <row r="579" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A579" s="1" t="s">
         <v>20</v>
       </c>
@@ -13802,7 +13802,7 @@
         <v>549.5</v>
       </c>
     </row>
-    <row r="580" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A580" s="1" t="s">
         <v>20</v>
       </c>
@@ -13825,7 +13825,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="581" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A581" s="1" t="s">
         <v>20</v>
       </c>
@@ -13848,7 +13848,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="582" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A582" s="1" t="s">
         <v>20</v>
       </c>
@@ -13871,7 +13871,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="583" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A583" s="1" t="s">
         <v>20</v>
       </c>
@@ -13894,7 +13894,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="584" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A584" s="1" t="s">
         <v>20</v>
       </c>
@@ -13917,7 +13917,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="585" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A585" s="1" t="s">
         <v>20</v>
       </c>
@@ -13940,7 +13940,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="586" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A586" s="1" t="s">
         <v>20</v>
       </c>
@@ -13963,7 +13963,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="587" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A587" s="1" t="s">
         <v>20</v>
       </c>
@@ -13986,7 +13986,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="588" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A588" s="1" t="s">
         <v>20</v>
       </c>
@@ -14009,7 +14009,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="589" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A589" s="1" t="s">
         <v>20</v>
       </c>
@@ -14032,7 +14032,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="590" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A590" s="1" t="s">
         <v>20</v>
       </c>
@@ -14055,7 +14055,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="591" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A591" s="1" t="s">
         <v>20</v>
       </c>
@@ -14078,7 +14078,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="592" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A592" s="1" t="s">
         <v>20</v>
       </c>
@@ -14101,7 +14101,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="593" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A593" s="1" t="s">
         <v>20</v>
       </c>
@@ -14124,7 +14124,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="594" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A594" s="1" t="s">
         <v>20</v>
       </c>
@@ -14147,7 +14147,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="595" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A595" s="1" t="s">
         <v>20</v>
       </c>
@@ -14170,7 +14170,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="596" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A596" s="1" t="s">
         <v>20</v>
       </c>
@@ -14193,7 +14193,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="597" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A597" s="1" t="s">
         <v>20</v>
       </c>
@@ -14216,7 +14216,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="598" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A598" s="1" t="s">
         <v>20</v>
       </c>
@@ -14239,7 +14239,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="599" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A599" s="1" t="s">
         <v>20</v>
       </c>
@@ -14262,7 +14262,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="600" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A600" s="1" t="s">
         <v>20</v>
       </c>
@@ -14285,7 +14285,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="601" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A601" s="1" t="s">
         <v>20</v>
       </c>
@@ -14308,7 +14308,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="602" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A602" s="1" t="s">
         <v>21</v>
       </c>
@@ -14331,7 +14331,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="603" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A603" s="1" t="s">
         <v>21</v>
       </c>
@@ -14354,7 +14354,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="604" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A604" s="1" t="s">
         <v>21</v>
       </c>
@@ -14377,7 +14377,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="605" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A605" s="1" t="s">
         <v>21</v>
       </c>
@@ -14400,7 +14400,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="606" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A606" s="1" t="s">
         <v>21</v>
       </c>
@@ -14423,7 +14423,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="607" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A607" s="1" t="s">
         <v>21</v>
       </c>
@@ -14446,7 +14446,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="608" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A608" s="1" t="s">
         <v>21</v>
       </c>
@@ -14469,7 +14469,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="609" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A609" s="1" t="s">
         <v>21</v>
       </c>
@@ -14492,7 +14492,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="610" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A610" s="1" t="s">
         <v>21</v>
       </c>
@@ -14515,7 +14515,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="611" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A611" s="1" t="s">
         <v>21</v>
       </c>
@@ -14538,7 +14538,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="612" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A612" s="1" t="s">
         <v>21</v>
       </c>
@@ -14561,7 +14561,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="613" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A613" s="1" t="s">
         <v>21</v>
       </c>
@@ -14584,7 +14584,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="614" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A614" s="1" t="s">
         <v>21</v>
       </c>
@@ -14607,7 +14607,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="615" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A615" s="1" t="s">
         <v>21</v>
       </c>
@@ -14630,7 +14630,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="616" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A616" s="1" t="s">
         <v>21</v>
       </c>
@@ -14653,7 +14653,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="617" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A617" s="1" t="s">
         <v>21</v>
       </c>
@@ -14676,7 +14676,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="618" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A618" s="1" t="s">
         <v>21</v>
       </c>
@@ -14699,7 +14699,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="619" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A619" s="1" t="s">
         <v>21</v>
       </c>
@@ -14722,7 +14722,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="620" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A620" s="1" t="s">
         <v>21</v>
       </c>
@@ -14745,7 +14745,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="621" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A621" s="1" t="s">
         <v>21</v>
       </c>
@@ -14768,7 +14768,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="622" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A622" s="1" t="s">
         <v>21</v>
       </c>
@@ -14791,7 +14791,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="623" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A623" s="1" t="s">
         <v>21</v>
       </c>
@@ -14814,7 +14814,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="624" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A624" s="1" t="s">
         <v>21</v>
       </c>
@@ -14837,7 +14837,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="625" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A625" s="1" t="s">
         <v>21</v>
       </c>
@@ -14860,7 +14860,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="626" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A626" s="1" t="s">
         <v>21</v>
       </c>
@@ -14883,7 +14883,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="627" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A627" s="1" t="s">
         <v>21</v>
       </c>
@@ -14906,7 +14906,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="628" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A628" s="1" t="s">
         <v>21</v>
       </c>
@@ -14929,7 +14929,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="629" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A629" s="1" t="s">
         <v>21</v>
       </c>
@@ -14952,7 +14952,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="630" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A630" s="1" t="s">
         <v>21</v>
       </c>
@@ -14975,7 +14975,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="631" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A631" s="1" t="s">
         <v>21</v>
       </c>
@@ -14998,7 +14998,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="632" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A632" s="1" t="s">
         <v>21</v>
       </c>
@@ -15021,7 +15021,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="633" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A633" s="1" t="s">
         <v>21</v>
       </c>
@@ -15044,7 +15044,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="634" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A634" s="1" t="s">
         <v>21</v>
       </c>
@@ -15067,7 +15067,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="635" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A635" s="1" t="s">
         <v>21</v>
       </c>
@@ -15090,7 +15090,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="636" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A636" s="1" t="s">
         <v>21</v>
       </c>
@@ -15113,7 +15113,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="637" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A637" s="1" t="s">
         <v>21</v>
       </c>
@@ -15136,7 +15136,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="638" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A638" s="1" t="s">
         <v>21</v>
       </c>
@@ -15159,7 +15159,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="639" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A639" s="1" t="s">
         <v>21</v>
       </c>
@@ -15182,7 +15182,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="640" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A640" s="1" t="s">
         <v>21</v>
       </c>
@@ -15205,7 +15205,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="641" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A641" s="1" t="s">
         <v>21</v>
       </c>
@@ -15228,7 +15228,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="642" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A642" s="1" t="s">
         <v>21</v>
       </c>
@@ -15251,7 +15251,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="643" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A643" s="1" t="s">
         <v>21</v>
       </c>
@@ -15274,7 +15274,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="644" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A644" s="1" t="s">
         <v>21</v>
       </c>
@@ -15297,7 +15297,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="645" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A645" s="1" t="s">
         <v>21</v>
       </c>
@@ -15320,7 +15320,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="646" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A646" s="1" t="s">
         <v>21</v>
       </c>
@@ -15343,7 +15343,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="647" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A647" s="1" t="s">
         <v>21</v>
       </c>
@@ -15366,7 +15366,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="648" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A648" s="1" t="s">
         <v>21</v>
       </c>
@@ -15389,7 +15389,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="649" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A649" s="1" t="s">
         <v>21</v>
       </c>
@@ -15412,7 +15412,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="650" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A650" s="1" t="s">
         <v>21</v>
       </c>
@@ -15435,7 +15435,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="651" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A651" s="1" t="s">
         <v>21</v>
       </c>
@@ -15458,7 +15458,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="652" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A652" s="1" t="s">
         <v>21</v>
       </c>
@@ -15481,7 +15481,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="653" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A653" s="1" t="s">
         <v>21</v>
       </c>
@@ -15504,7 +15504,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="654" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A654" s="1" t="s">
         <v>21</v>
       </c>
@@ -15527,7 +15527,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="655" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A655" s="1" t="s">
         <v>21</v>
       </c>
@@ -15550,7 +15550,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="656" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A656" s="1" t="s">
         <v>21</v>
       </c>
@@ -15573,7 +15573,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="657" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A657" s="1" t="s">
         <v>21</v>
       </c>
@@ -15596,7 +15596,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="658" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A658" s="1" t="s">
         <v>21</v>
       </c>
@@ -15619,7 +15619,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="659" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A659" s="1" t="s">
         <v>21</v>
       </c>
@@ -15642,7 +15642,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="660" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A660" s="1" t="s">
         <v>21</v>
       </c>
@@ -15665,7 +15665,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="661" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A661" s="1" t="s">
         <v>21</v>
       </c>
@@ -15688,7 +15688,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="662" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A662" s="1" t="s">
         <v>21</v>
       </c>
@@ -15711,7 +15711,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="663" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A663" s="1" t="s">
         <v>21</v>
       </c>
@@ -15734,7 +15734,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="664" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A664" s="1" t="s">
         <v>21</v>
       </c>
@@ -15757,7 +15757,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="665" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A665" s="1" t="s">
         <v>21</v>
       </c>
@@ -15780,7 +15780,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="666" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A666" s="1" t="s">
         <v>21</v>
       </c>
@@ -15803,7 +15803,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="667" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A667" s="1" t="s">
         <v>21</v>
       </c>
@@ -15826,7 +15826,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="668" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A668" s="1" t="s">
         <v>21</v>
       </c>
@@ -15849,7 +15849,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="669" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A669" s="1" t="s">
         <v>21</v>
       </c>
@@ -15872,7 +15872,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="670" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A670" s="1" t="s">
         <v>21</v>
       </c>
@@ -15895,7 +15895,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="671" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A671" s="1" t="s">
         <v>21</v>
       </c>
@@ -15918,7 +15918,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="672" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A672" s="1" t="s">
         <v>21</v>
       </c>
@@ -15941,7 +15941,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="673" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A673" s="1" t="s">
         <v>21</v>
       </c>
@@ -15964,7 +15964,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="674" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A674" s="1" t="s">
         <v>21</v>
       </c>
@@ -15987,7 +15987,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="675" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A675" s="1" t="s">
         <v>21</v>
       </c>
@@ -16010,7 +16010,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="676" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A676" s="1" t="s">
         <v>21</v>
       </c>
@@ -16033,7 +16033,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="677" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A677" s="1" t="s">
         <v>21</v>
       </c>
@@ -16056,7 +16056,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="678" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A678" s="1" t="s">
         <v>21</v>
       </c>
@@ -16079,7 +16079,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="679" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="679" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A679" s="1" t="s">
         <v>21</v>
       </c>
@@ -16102,7 +16102,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="680" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="680" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A680" s="1" t="s">
         <v>21</v>
       </c>
@@ -16125,7 +16125,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="681" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="681" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A681" s="1" t="s">
         <v>21</v>
       </c>
@@ -16148,7 +16148,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="682" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="682" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A682" s="1" t="s">
         <v>21</v>
       </c>
@@ -16171,7 +16171,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="683" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="683" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A683" s="1" t="s">
         <v>21</v>
       </c>
@@ -16194,7 +16194,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="684" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="684" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A684" s="1" t="s">
         <v>21</v>
       </c>
@@ -16217,7 +16217,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="685" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="685" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A685" s="1" t="s">
         <v>21</v>
       </c>
@@ -16240,7 +16240,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="686" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A686" s="1" t="s">
         <v>21</v>
       </c>
@@ -16263,7 +16263,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="687" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="687" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A687" s="1" t="s">
         <v>21</v>
       </c>
@@ -16286,7 +16286,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="688" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A688" s="1" t="s">
         <v>21</v>
       </c>
@@ -16309,7 +16309,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="689" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A689" s="1" t="s">
         <v>21</v>
       </c>
@@ -16332,7 +16332,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="690" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A690" s="1" t="s">
         <v>21</v>
       </c>
@@ -16355,7 +16355,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="691" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A691" s="1" t="s">
         <v>21</v>
       </c>
@@ -16378,7 +16378,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="692" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A692" s="1" t="s">
         <v>21</v>
       </c>
@@ -16401,7 +16401,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="693" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="693" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A693" s="1" t="s">
         <v>21</v>
       </c>
@@ -16424,7 +16424,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="694" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A694" s="1" t="s">
         <v>21</v>
       </c>
@@ -16447,7 +16447,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="695" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A695" s="1" t="s">
         <v>21</v>
       </c>
@@ -16470,7 +16470,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="696" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A696" s="1" t="s">
         <v>21</v>
       </c>
@@ -16493,7 +16493,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="697" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A697" s="1" t="s">
         <v>21</v>
       </c>
@@ -16516,7 +16516,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="698" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="698" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A698" s="1" t="s">
         <v>21</v>
       </c>
@@ -16539,7 +16539,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="699" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="699" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A699" s="1" t="s">
         <v>21</v>
       </c>
@@ -16562,7 +16562,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="700" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="700" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A700" s="1" t="s">
         <v>21</v>
       </c>
@@ -16585,7 +16585,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="701" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="701" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A701" s="1" t="s">
         <v>21</v>
       </c>
@@ -16608,7 +16608,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="702" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="702" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A702" s="1" t="s">
         <v>21</v>
       </c>
@@ -16631,7 +16631,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="703" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="703" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A703" s="1" t="s">
         <v>21</v>
       </c>
@@ -16654,7 +16654,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="704" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="704" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A704" s="1" t="s">
         <v>21</v>
       </c>
@@ -16677,7 +16677,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="705" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="705" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A705" s="1" t="s">
         <v>21</v>
       </c>
@@ -16700,7 +16700,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="706" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="706" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A706" s="1" t="s">
         <v>21</v>
       </c>
@@ -16723,7 +16723,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="707" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="707" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A707" s="1" t="s">
         <v>21</v>
       </c>
@@ -16746,7 +16746,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="708" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="708" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A708" s="1" t="s">
         <v>21</v>
       </c>
@@ -16769,7 +16769,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="709" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="709" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A709" s="1" t="s">
         <v>21</v>
       </c>
@@ -16792,7 +16792,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="710" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="710" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A710" s="1" t="s">
         <v>21</v>
       </c>
@@ -16815,7 +16815,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="711" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="711" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A711" s="1" t="s">
         <v>21</v>
       </c>
@@ -16838,7 +16838,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="712" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="712" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A712" s="1" t="s">
         <v>21</v>
       </c>
@@ -16861,7 +16861,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="713" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="713" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A713" s="1" t="s">
         <v>21</v>
       </c>
@@ -16884,7 +16884,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="714" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="714" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A714" s="1" t="s">
         <v>21</v>
       </c>
@@ -16907,7 +16907,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="715" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="715" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A715" s="1" t="s">
         <v>21</v>
       </c>
@@ -16930,7 +16930,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="716" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="716" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A716" s="1" t="s">
         <v>21</v>
       </c>
@@ -16953,7 +16953,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="717" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="717" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A717" s="1" t="s">
         <v>21</v>
       </c>
@@ -16976,7 +16976,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="718" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="718" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A718" s="1" t="s">
         <v>21</v>
       </c>
@@ -16999,7 +16999,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="719" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="719" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A719" s="1" t="s">
         <v>21</v>
       </c>
@@ -17022,7 +17022,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="720" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="720" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A720" s="1" t="s">
         <v>21</v>
       </c>
@@ -17045,7 +17045,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="721" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="721" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A721" s="1" t="s">
         <v>21</v>
       </c>
@@ -17068,7 +17068,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="722" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="722" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A722" s="1" t="s">
         <v>21</v>
       </c>
@@ -17091,7 +17091,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="723" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="723" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A723" s="1" t="s">
         <v>21</v>
       </c>
@@ -17114,7 +17114,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="724" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="724" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A724" s="1" t="s">
         <v>21</v>
       </c>
@@ -17137,7 +17137,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="725" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="725" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A725" s="1" t="s">
         <v>21</v>
       </c>
@@ -17160,7 +17160,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="726" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="726" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A726" s="1" t="s">
         <v>21</v>
       </c>
@@ -17183,7 +17183,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="727" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="727" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A727" s="1" t="s">
         <v>21</v>
       </c>
@@ -17206,7 +17206,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="728" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="728" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A728" s="1" t="s">
         <v>21</v>
       </c>
@@ -17229,7 +17229,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="729" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="729" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A729" s="1" t="s">
         <v>21</v>
       </c>
@@ -17252,7 +17252,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="730" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="730" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A730" s="1" t="s">
         <v>21</v>
       </c>
@@ -17275,7 +17275,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="731" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="731" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A731" s="1" t="s">
         <v>21</v>
       </c>
@@ -17298,7 +17298,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="732" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="732" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A732" s="1" t="s">
         <v>21</v>
       </c>
@@ -17321,7 +17321,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="733" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="733" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A733" s="1" t="s">
         <v>21</v>
       </c>
@@ -17344,7 +17344,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="734" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="734" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A734" s="1" t="s">
         <v>21</v>
       </c>
@@ -17367,7 +17367,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="735" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="735" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A735" s="1" t="s">
         <v>21</v>
       </c>
@@ -17390,7 +17390,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="736" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="736" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A736" s="1" t="s">
         <v>21</v>
       </c>
@@ -17413,7 +17413,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="737" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="737" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A737" s="1" t="s">
         <v>21</v>
       </c>
@@ -17436,7 +17436,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="738" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="738" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A738" s="1" t="s">
         <v>21</v>
       </c>
@@ -17459,7 +17459,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="739" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="739" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A739" s="1" t="s">
         <v>21</v>
       </c>
@@ -17482,7 +17482,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="740" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="740" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A740" s="1" t="s">
         <v>21</v>
       </c>
@@ -17505,7 +17505,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="741" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="741" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A741" s="1" t="s">
         <v>21</v>
       </c>
@@ -17528,7 +17528,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="742" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="742" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A742" s="1" t="s">
         <v>21</v>
       </c>
@@ -17551,7 +17551,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="743" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="743" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A743" s="1" t="s">
         <v>21</v>
       </c>
@@ -17574,7 +17574,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="744" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="744" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A744" s="1" t="s">
         <v>21</v>
       </c>
@@ -17597,7 +17597,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="745" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="745" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A745" s="1" t="s">
         <v>21</v>
       </c>
@@ -17620,7 +17620,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="746" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="746" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A746" s="1" t="s">
         <v>21</v>
       </c>
@@ -17643,7 +17643,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="747" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="747" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A747" s="1" t="s">
         <v>21</v>
       </c>
@@ -17666,7 +17666,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="748" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="748" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A748" s="1" t="s">
         <v>21</v>
       </c>
@@ -17689,7 +17689,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="749" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="749" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A749" s="1" t="s">
         <v>21</v>
       </c>
@@ -17712,7 +17712,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="750" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="750" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A750" s="1" t="s">
         <v>21</v>
       </c>
@@ -17735,7 +17735,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="751" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="751" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A751" s="1" t="s">
         <v>21</v>
       </c>
@@ -17758,7 +17758,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="752" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="752" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A752" s="1" t="s">
         <v>21</v>
       </c>
@@ -17781,7 +17781,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="753" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="753" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A753" s="1" t="s">
         <v>21</v>
       </c>
@@ -17804,7 +17804,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="754" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="754" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A754" s="1" t="s">
         <v>21</v>
       </c>
@@ -17827,7 +17827,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="755" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="755" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A755" s="1" t="s">
         <v>21</v>
       </c>
@@ -17850,7 +17850,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="756" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="756" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A756" s="1" t="s">
         <v>21</v>
       </c>
@@ -17873,7 +17873,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="757" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="757" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A757" s="1" t="s">
         <v>21</v>
       </c>
@@ -17896,7 +17896,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="758" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="758" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A758" s="1" t="s">
         <v>21</v>
       </c>
@@ -17919,7 +17919,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="759" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="759" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A759" s="1" t="s">
         <v>21</v>
       </c>
@@ -17942,7 +17942,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="760" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="760" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A760" s="1" t="s">
         <v>21</v>
       </c>
@@ -17965,7 +17965,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="761" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="761" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A761" s="1" t="s">
         <v>21</v>
       </c>
@@ -17988,7 +17988,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="762" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="762" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A762" s="1" t="s">
         <v>21</v>
       </c>
@@ -18011,7 +18011,7 @@
         <v>678.5</v>
       </c>
     </row>
-    <row r="763" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="763" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A763" s="1" t="s">
         <v>21</v>
       </c>
@@ -18034,7 +18034,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="764" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="764" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A764" s="1" t="s">
         <v>21</v>
       </c>
@@ -18057,7 +18057,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="765" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="765" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A765" s="1" t="s">
         <v>21</v>
       </c>
@@ -18080,7 +18080,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="766" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="766" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A766" s="1" t="s">
         <v>21</v>
       </c>
@@ -18103,7 +18103,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="767" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="767" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A767" s="1" t="s">
         <v>21</v>
       </c>
@@ -18126,7 +18126,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="768" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="768" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A768" s="1" t="s">
         <v>21</v>
       </c>
@@ -18149,7 +18149,7 @@
         <v>569.5</v>
       </c>
     </row>
-    <row r="769" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="769" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A769" s="1" t="s">
         <v>21</v>
       </c>
@@ -18172,7 +18172,7 @@
         <v>700.5</v>
       </c>
     </row>
-    <row r="770" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="770" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A770" s="1" t="s">
         <v>21</v>
       </c>
@@ -18195,7 +18195,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="771" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="771" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A771" s="1" t="s">
         <v>21</v>
       </c>
@@ -18218,7 +18218,7 @@
         <v>556.5</v>
       </c>
     </row>
-    <row r="772" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="772" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A772" s="1" t="s">
         <v>21</v>
       </c>
@@ -18241,7 +18241,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="773" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="773" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A773" s="1" t="s">
         <v>21</v>
       </c>
@@ -18264,7 +18264,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="774" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="774" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A774" s="1" t="s">
         <v>21</v>
       </c>
@@ -18287,7 +18287,7 @@
         <v>770.5</v>
       </c>
     </row>
-    <row r="775" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="775" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A775" s="1" t="s">
         <v>21</v>
       </c>
@@ -18310,7 +18310,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="776" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="776" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A776" s="1" t="s">
         <v>21</v>
       </c>
@@ -18333,7 +18333,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="777" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="777" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A777" s="1" t="s">
         <v>21</v>
       </c>
@@ -18356,7 +18356,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="778" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="778" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A778" s="1" t="s">
         <v>21</v>
       </c>
@@ -18379,7 +18379,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="779" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="779" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A779" s="1" t="s">
         <v>21</v>
       </c>
@@ -18402,7 +18402,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="780" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="780" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A780" s="1" t="s">
         <v>21</v>
       </c>
@@ -18425,7 +18425,7 @@
         <v>655.5</v>
       </c>
     </row>
-    <row r="781" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="781" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A781" s="1" t="s">
         <v>21</v>
       </c>
@@ -18448,7 +18448,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="782" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="782" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A782" s="1" t="s">
         <v>21</v>
       </c>
@@ -18471,7 +18471,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="783" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="783" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A783" s="1" t="s">
         <v>21</v>
       </c>
@@ -18494,7 +18494,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="784" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="784" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A784" s="1" t="s">
         <v>21</v>
       </c>
@@ -18517,7 +18517,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="785" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="785" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A785" s="1" t="s">
         <v>21</v>
       </c>
@@ -18540,7 +18540,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="786" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="786" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A786" s="1" t="s">
         <v>21</v>
       </c>
@@ -18563,7 +18563,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="787" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="787" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A787" s="1" t="s">
         <v>21</v>
       </c>
@@ -18586,7 +18586,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="788" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="788" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A788" s="1" t="s">
         <v>21</v>
       </c>
@@ -18609,7 +18609,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="789" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="789" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A789" s="1" t="s">
         <v>21</v>
       </c>
@@ -18632,7 +18632,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="790" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="790" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A790" s="1" t="s">
         <v>21</v>
       </c>
@@ -18655,7 +18655,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="791" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="791" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A791" s="1" t="s">
         <v>21</v>
       </c>
@@ -18678,7 +18678,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="792" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="792" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A792" s="1" t="s">
         <v>21</v>
       </c>
@@ -18701,7 +18701,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="793" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="793" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A793" s="1" t="s">
         <v>21</v>
       </c>
@@ -18724,7 +18724,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="794" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="794" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A794" s="1" t="s">
         <v>21</v>
       </c>
@@ -18747,7 +18747,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="795" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="795" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A795" s="1" t="s">
         <v>21</v>
       </c>
@@ -18770,7 +18770,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="796" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="796" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A796" s="1" t="s">
         <v>21</v>
       </c>
@@ -18793,7 +18793,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="797" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="797" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A797" s="1" t="s">
         <v>21</v>
       </c>
@@ -18816,7 +18816,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="798" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="798" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A798" s="1" t="s">
         <v>21</v>
       </c>
@@ -18839,7 +18839,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="799" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="799" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A799" s="1" t="s">
         <v>21</v>
       </c>
@@ -18862,7 +18862,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="800" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="800" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A800" s="1" t="s">
         <v>21</v>
       </c>
@@ -18885,7 +18885,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="801" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="801" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A801" s="1" t="s">
         <v>21</v>
       </c>
